--- a/SCE407-2025-2026-T2.xlsx
+++ b/SCE407-2025-2026-T2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misbar907-my.sharepoint.com/personal/nehad_misbar-tech_com/Documents/Share/SCE407-SWE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misbar907-my.sharepoint.com/personal/nehad_misbar-tech_com/Documents/Private/Azhar/SWE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F290F962-A262-4426-A2ED-55B6198474A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98943060-4374-4493-A54D-3B298975C858}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{F290F962-A262-4426-A2ED-55B6198474A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDAE865C-EF2A-4CBA-A8DC-FAC23E48874D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="16220" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1213,7 +1213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1364,21 +1364,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1733,11 +1718,11 @@
         <v>12</v>
       </c>
       <c r="I2" s="53">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4">
         <f>SUM(F2:I2)</f>
-        <v>24</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1765,12 +1750,12 @@
       <c r="H3" s="3">
         <v>24</v>
       </c>
-      <c r="I3" s="51">
-        <v>7</v>
+      <c r="I3" s="53">
+        <v>7.5</v>
       </c>
       <c r="J3" s="4">
-        <f t="shared" ref="J3:J66" si="0">SUM(F3:I3)</f>
-        <v>43.75</v>
+        <f>SUM(F3:I3)</f>
+        <v>44.25</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1799,11 +1784,11 @@
         <v>23</v>
       </c>
       <c r="I4" s="53">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="J4" s="4">
         <f>SUM(F4:I4)</f>
-        <v>38.75</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1832,11 +1817,11 @@
         <v>21</v>
       </c>
       <c r="I5" s="53">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J5" s="4">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(F5:I5)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1865,11 +1850,11 @@
         <v>21</v>
       </c>
       <c r="I6" s="53">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J6" s="4">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(F6:I6)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1898,11 +1883,11 @@
         <v>20</v>
       </c>
       <c r="I7" s="53">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J7" s="4">
-        <f t="shared" si="0"/>
-        <v>41.5</v>
+        <f>SUM(F7:I7)</f>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1931,11 +1916,11 @@
         <v>25</v>
       </c>
       <c r="I8" s="53">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4">
-        <f t="shared" si="0"/>
-        <v>43.75</v>
+        <f>SUM(F8:I8)</f>
+        <v>44.25</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1964,11 +1949,11 @@
         <v>25</v>
       </c>
       <c r="I9" s="53">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>SUM(F9:I9)</f>
+        <v>47.5</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -1997,11 +1982,11 @@
         <v>25</v>
       </c>
       <c r="I10" s="53">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(F10:I10)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2030,11 +2015,11 @@
         <v>17</v>
       </c>
       <c r="I11" s="53">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="J11" s="4">
-        <f t="shared" si="0"/>
-        <v>35.75</v>
+        <f>SUM(F11:I11)</f>
+        <v>36.25</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2061,11 +2046,11 @@
         <v>25</v>
       </c>
       <c r="I12" s="53">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="0"/>
-        <v>42.5</v>
+        <f>SUM(F12:I12)</f>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2092,11 +2077,11 @@
         <v>20</v>
       </c>
       <c r="I13" s="53">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" si="0"/>
-        <v>40.25</v>
+        <f>SUM(F13:I13)</f>
+        <v>40.75</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2125,11 +2110,11 @@
         <v>17</v>
       </c>
       <c r="I14" s="53">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4">
-        <f t="shared" si="0"/>
-        <v>32.5</v>
+        <f>SUM(F14:I14)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2156,11 +2141,11 @@
         <v>12</v>
       </c>
       <c r="I15" s="53">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f>SUM(F15:I15)</f>
+        <v>27.5</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2189,11 +2174,11 @@
         <v>21</v>
       </c>
       <c r="I16" s="53">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="0"/>
-        <v>36.75</v>
+        <f>SUM(F16:I16)</f>
+        <v>37.25</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2213,7 +2198,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G17" s="3">
         <v>5</v>
@@ -2222,11 +2207,11 @@
         <v>20</v>
       </c>
       <c r="I17" s="53">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4">
-        <f t="shared" si="0"/>
-        <v>41.5</v>
+        <f>SUM(F17:I17)</f>
+        <v>42.5</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2246,7 +2231,7 @@
         <v>16</v>
       </c>
       <c r="F18" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G18" s="3">
         <v>2.5</v>
@@ -2255,11 +2240,11 @@
         <v>22</v>
       </c>
       <c r="I18" s="53">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <f>SUM(F18:I18)</f>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2279,7 +2264,7 @@
         <v>16</v>
       </c>
       <c r="F19" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G19" s="3">
         <v>3.5</v>
@@ -2288,11 +2273,11 @@
         <v>21</v>
       </c>
       <c r="I19" s="53">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" si="0"/>
-        <v>41</v>
+        <f>SUM(F19:I19)</f>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2312,7 +2297,7 @@
         <v>8</v>
       </c>
       <c r="F20" s="4">
-        <v>3.5</v>
+        <v>8.25</v>
       </c>
       <c r="G20" s="3">
         <v>5</v>
@@ -2321,11 +2306,11 @@
         <v>20</v>
       </c>
       <c r="I20" s="53">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <f>SUM(F20:I20)</f>
+        <v>38.25</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2354,11 +2339,11 @@
         <v>19</v>
       </c>
       <c r="I21" s="53">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="0"/>
-        <v>32.75</v>
+        <f>SUM(F21:I21)</f>
+        <v>33.25</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2387,11 +2372,11 @@
         <v>24</v>
       </c>
       <c r="I22" s="53">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" si="0"/>
-        <v>46</v>
+        <f>SUM(F22:I22)</f>
+        <v>46.5</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2420,11 +2405,11 @@
         <v>25</v>
       </c>
       <c r="I23" s="53">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(F23:I23)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2453,11 +2438,11 @@
         <v>23</v>
       </c>
       <c r="I24" s="53">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f>SUM(F24:I24)</f>
+        <v>39.5</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2477,7 +2462,7 @@
         <v>16</v>
       </c>
       <c r="F25" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G25" s="3">
         <v>2.5</v>
@@ -2486,11 +2471,11 @@
         <v>18</v>
       </c>
       <c r="I25" s="53">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" si="0"/>
-        <v>32.5</v>
+        <f>SUM(F25:I25)</f>
+        <v>33.5</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2519,11 +2504,11 @@
         <v>21</v>
       </c>
       <c r="I26" s="53">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="0"/>
-        <v>39.25</v>
+        <f>SUM(F26:I26)</f>
+        <v>39.75</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -2551,12 +2536,12 @@
       <c r="H27" s="33">
         <v>19</v>
       </c>
-      <c r="I27" s="54">
-        <v>9.75</v>
+      <c r="I27" s="53">
+        <v>10.25</v>
       </c>
       <c r="J27" s="32">
-        <f t="shared" si="0"/>
-        <v>41.75</v>
+        <f>SUM(F27:I27)</f>
+        <v>42.25</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -2584,12 +2569,12 @@
       <c r="H28" s="26">
         <v>23</v>
       </c>
-      <c r="I28" s="55">
-        <v>2</v>
+      <c r="I28" s="53">
+        <v>2.5</v>
       </c>
       <c r="J28" s="25">
-        <f t="shared" si="0"/>
-        <v>33.5</v>
+        <f>SUM(F28:I28)</f>
+        <v>34</v>
       </c>
       <c r="K28" s="27"/>
       <c r="L28" s="28"/>
@@ -2619,12 +2604,12 @@
       <c r="H29" s="37">
         <v>16</v>
       </c>
-      <c r="I29" s="56">
-        <v>9.5</v>
+      <c r="I29" s="53">
+        <v>10</v>
       </c>
       <c r="J29" s="36">
-        <f t="shared" si="0"/>
-        <v>36.25</v>
+        <f>SUM(F29:I29)</f>
+        <v>36.75</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2653,11 +2638,11 @@
         <v>22</v>
       </c>
       <c r="I30" s="53">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J30" s="4">
-        <f t="shared" si="0"/>
-        <v>43</v>
+        <f>SUM(F30:I30)</f>
+        <v>43.5</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2686,11 +2671,11 @@
         <v>24</v>
       </c>
       <c r="I31" s="53">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J31" s="4">
-        <f t="shared" si="0"/>
-        <v>41.5</v>
+        <f>SUM(F31:I31)</f>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2719,11 +2704,11 @@
         <v>18</v>
       </c>
       <c r="I32" s="53">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4">
-        <f t="shared" si="0"/>
-        <v>37.5</v>
+        <f>SUM(F32:I32)</f>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2752,11 +2737,11 @@
         <v>18</v>
       </c>
       <c r="I33" s="53">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4">
-        <f t="shared" si="0"/>
-        <v>38.75</v>
+        <f>SUM(F33:I33)</f>
+        <v>39.25</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2785,11 +2770,11 @@
         <v>15</v>
       </c>
       <c r="I34" s="53">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4">
-        <f t="shared" si="0"/>
-        <v>29.5</v>
+        <f>SUM(F34:I34)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2816,11 +2801,11 @@
         <v>16</v>
       </c>
       <c r="I35" s="53">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4">
-        <f t="shared" si="0"/>
-        <v>30.25</v>
+        <f>SUM(F35:I35)</f>
+        <v>30.75</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2849,11 +2834,11 @@
         <v>22</v>
       </c>
       <c r="I36" s="53">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4">
-        <f t="shared" si="0"/>
-        <v>40.75</v>
+        <f>SUM(F36:I36)</f>
+        <v>41.25</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2882,11 +2867,11 @@
         <v>17</v>
       </c>
       <c r="I37" s="53">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J37" s="4">
-        <f t="shared" si="0"/>
-        <v>35.75</v>
+        <f>SUM(F37:I37)</f>
+        <v>36.25</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2915,11 +2900,11 @@
         <v>24</v>
       </c>
       <c r="I38" s="53">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J38" s="4">
-        <f t="shared" si="0"/>
-        <v>45</v>
+        <f>SUM(F38:I38)</f>
+        <v>45.5</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2948,11 +2933,11 @@
         <v>20</v>
       </c>
       <c r="I39" s="53">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J39" s="4">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <f>SUM(F39:I39)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -2981,11 +2966,11 @@
         <v>16</v>
       </c>
       <c r="I40" s="53">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J40" s="4">
-        <f t="shared" si="0"/>
-        <v>34.25</v>
+        <f>SUM(F40:I40)</f>
+        <v>34.75</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3014,11 +2999,11 @@
         <v>22</v>
       </c>
       <c r="I41" s="53">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="J41" s="4">
-        <f t="shared" si="0"/>
-        <v>40.25</v>
+        <f>SUM(F41:I41)</f>
+        <v>40.75</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3047,11 +3032,11 @@
         <v>18</v>
       </c>
       <c r="I42" s="53">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J42" s="4">
-        <f t="shared" si="0"/>
-        <v>38.25</v>
+        <f>SUM(F42:I42)</f>
+        <v>38.75</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3080,11 +3065,11 @@
         <v>20</v>
       </c>
       <c r="I43" s="53">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f>SUM(F43:I43)</f>
+        <v>39.5</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3113,11 +3098,11 @@
         <v>23</v>
       </c>
       <c r="I44" s="53">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J44" s="4">
-        <f t="shared" si="0"/>
-        <v>44</v>
+        <f>SUM(F44:I44)</f>
+        <v>44.5</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3146,11 +3131,11 @@
         <v>21</v>
       </c>
       <c r="I45" s="53">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4">
-        <f t="shared" si="0"/>
-        <v>38.75</v>
+        <f>SUM(F45:I45)</f>
+        <v>39.25</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3179,11 +3164,11 @@
         <v>17</v>
       </c>
       <c r="I46" s="53">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <f>SUM(F46:I46)</f>
+        <v>32.25</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3210,11 +3195,11 @@
         <v>24</v>
       </c>
       <c r="I47" s="53">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4">
-        <f t="shared" si="0"/>
-        <v>44.75</v>
+        <f>SUM(F47:I47)</f>
+        <v>45.25</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3243,11 +3228,11 @@
         <v>21</v>
       </c>
       <c r="I48" s="53">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J48" s="4">
-        <f t="shared" si="0"/>
-        <v>40.5</v>
+        <f>SUM(F48:I48)</f>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3276,11 +3261,11 @@
         <v>16</v>
       </c>
       <c r="I49" s="53">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J49" s="4">
-        <f t="shared" si="0"/>
-        <v>34.5</v>
+        <f>SUM(F49:I49)</f>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3309,11 +3294,11 @@
         <v>25</v>
       </c>
       <c r="I50" s="53">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4">
-        <f t="shared" si="0"/>
-        <v>45.25</v>
+        <f>SUM(F50:I50)</f>
+        <v>45.75</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3342,11 +3327,11 @@
         <v>21</v>
       </c>
       <c r="I51" s="53">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J51" s="4">
-        <f t="shared" si="0"/>
-        <v>34.75</v>
+        <f>SUM(F51:I51)</f>
+        <v>35.25</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3375,11 +3360,11 @@
         <v>18</v>
       </c>
       <c r="I52" s="53">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J52" s="4">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <f>SUM(F52:I52)</f>
+        <v>36.5</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3408,11 +3393,11 @@
         <v>19</v>
       </c>
       <c r="I53" s="53">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J53" s="4">
-        <f t="shared" si="0"/>
-        <v>36.75</v>
+        <f>SUM(F53:I53)</f>
+        <v>37.25</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3441,11 +3426,11 @@
         <v>25</v>
       </c>
       <c r="I54" s="53">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4">
-        <f t="shared" si="0"/>
-        <v>43.5</v>
+        <f>SUM(F54:I54)</f>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3474,11 +3459,11 @@
         <v>22</v>
       </c>
       <c r="I55" s="53">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J55" s="4">
-        <f t="shared" si="0"/>
-        <v>40.25</v>
+        <f>SUM(F55:I55)</f>
+        <v>40.75</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3500,11 +3485,11 @@
         <v>4.5</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="57">
+      <c r="I56" s="53">
         <v>1</v>
       </c>
       <c r="J56" s="4">
-        <f t="shared" si="0"/>
+        <f>SUM(F56:I56)</f>
         <v>5.5</v>
       </c>
     </row>
@@ -3529,12 +3514,12 @@
       <c r="H57" s="3">
         <v>21</v>
       </c>
-      <c r="I57" s="57">
-        <v>7.5</v>
+      <c r="I57" s="53">
+        <v>8</v>
       </c>
       <c r="J57" s="4">
-        <f t="shared" si="0"/>
-        <v>36.75</v>
+        <f>SUM(F57:I57)</f>
+        <v>37.25</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3562,12 +3547,12 @@
       <c r="H58" s="3">
         <v>23</v>
       </c>
-      <c r="I58" s="57">
-        <v>8</v>
+      <c r="I58" s="53">
+        <v>8.5</v>
       </c>
       <c r="J58" s="4">
-        <f t="shared" si="0"/>
-        <v>44.5</v>
+        <f>SUM(F58:I58)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3595,12 +3580,12 @@
       <c r="H59" s="20">
         <v>21</v>
       </c>
-      <c r="I59" s="57">
-        <v>2.75</v>
+      <c r="I59" s="53">
+        <v>3.25</v>
       </c>
       <c r="J59" s="4">
-        <f t="shared" si="0"/>
-        <v>33.75</v>
+        <f>SUM(F59:I59)</f>
+        <v>34.25</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3628,12 +3613,12 @@
       <c r="H60" s="20">
         <v>21</v>
       </c>
-      <c r="I60" s="57">
-        <v>9</v>
+      <c r="I60" s="53">
+        <v>9.5</v>
       </c>
       <c r="J60" s="4">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <f>SUM(F60:I60)</f>
+        <v>42.5</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3661,12 +3646,12 @@
       <c r="H61" s="3">
         <v>20</v>
       </c>
-      <c r="I61" s="57">
-        <v>8</v>
+      <c r="I61" s="53">
+        <v>8.5</v>
       </c>
       <c r="J61" s="4">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <f>SUM(F61:I61)</f>
+        <v>39.5</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3694,12 +3679,12 @@
       <c r="H62" s="3">
         <v>22</v>
       </c>
-      <c r="I62" s="57">
-        <v>5</v>
+      <c r="I62" s="53">
+        <v>5.5</v>
       </c>
       <c r="J62" s="4">
-        <f t="shared" si="0"/>
-        <v>40.5</v>
+        <f>SUM(F62:I62)</f>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3727,12 +3712,12 @@
       <c r="H63" s="20">
         <v>23</v>
       </c>
-      <c r="I63" s="57">
-        <v>4</v>
+      <c r="I63" s="53">
+        <v>9.5</v>
       </c>
       <c r="J63" s="4">
-        <f t="shared" si="0"/>
-        <v>41.5</v>
+        <f>SUM(F63:I63)</f>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3760,12 +3745,12 @@
       <c r="H64" s="3">
         <v>23</v>
       </c>
-      <c r="I64" s="57">
-        <v>8.5</v>
+      <c r="I64" s="53">
+        <v>9</v>
       </c>
       <c r="J64" s="4">
-        <f t="shared" si="0"/>
-        <v>45</v>
+        <f>SUM(F64:I64)</f>
+        <v>45.5</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3793,12 +3778,12 @@
       <c r="H65" s="3">
         <v>19</v>
       </c>
-      <c r="I65" s="57">
-        <v>3</v>
+      <c r="I65" s="53">
+        <v>3.5</v>
       </c>
       <c r="J65" s="4">
-        <f t="shared" si="0"/>
-        <v>36.5</v>
+        <f>SUM(F65:I65)</f>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3826,12 +3811,12 @@
       <c r="H66" s="3">
         <v>20</v>
       </c>
-      <c r="I66" s="57">
-        <v>8.5</v>
+      <c r="I66" s="53">
+        <v>9</v>
       </c>
       <c r="J66" s="4">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <f>SUM(F66:I66)</f>
+        <v>42.5</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3859,12 +3844,12 @@
       <c r="H67" s="3">
         <v>13</v>
       </c>
-      <c r="I67" s="57">
-        <v>6</v>
+      <c r="I67" s="53">
+        <v>6.5</v>
       </c>
       <c r="J67" s="4">
-        <f t="shared" ref="J67:J130" si="1">SUM(F67:I67)</f>
-        <v>29.75</v>
+        <f>SUM(F67:I67)</f>
+        <v>30.25</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3890,12 +3875,12 @@
       <c r="H68" s="3">
         <v>24</v>
       </c>
-      <c r="I68" s="57">
-        <v>7.5</v>
+      <c r="I68" s="53">
+        <v>8</v>
       </c>
       <c r="J68" s="4">
-        <f t="shared" si="1"/>
-        <v>45.25</v>
+        <f>SUM(F68:I68)</f>
+        <v>45.75</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3923,12 +3908,12 @@
       <c r="H69" s="3">
         <v>24</v>
       </c>
-      <c r="I69" s="57">
-        <v>9</v>
+      <c r="I69" s="53">
+        <v>9.5</v>
       </c>
       <c r="J69" s="4">
-        <f t="shared" si="1"/>
-        <v>46.25</v>
+        <f>SUM(F69:I69)</f>
+        <v>46.75</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3956,12 +3941,12 @@
       <c r="H70" s="3">
         <v>23</v>
       </c>
-      <c r="I70" s="57">
-        <v>7.5</v>
+      <c r="I70" s="53">
+        <v>8</v>
       </c>
       <c r="J70" s="4">
-        <f t="shared" si="1"/>
-        <v>42.75</v>
+        <f>SUM(F70:I70)</f>
+        <v>43.25</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -3989,12 +3974,12 @@
       <c r="H71" s="3">
         <v>14</v>
       </c>
-      <c r="I71" s="57">
-        <v>9.5</v>
+      <c r="I71" s="53">
+        <v>10</v>
       </c>
       <c r="J71" s="4">
-        <f t="shared" si="1"/>
-        <v>35.5</v>
+        <f>SUM(F71:I71)</f>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4022,12 +4007,12 @@
       <c r="H72" s="3">
         <v>21</v>
       </c>
-      <c r="I72" s="57">
-        <v>5</v>
+      <c r="I72" s="53">
+        <v>5.5</v>
       </c>
       <c r="J72" s="4">
-        <f t="shared" si="1"/>
-        <v>35.5</v>
+        <f>SUM(F72:I72)</f>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4055,12 +4040,12 @@
       <c r="H73" s="3">
         <v>16</v>
       </c>
-      <c r="I73" s="57">
-        <v>2.5</v>
+      <c r="I73" s="53">
+        <v>3</v>
       </c>
       <c r="J73" s="4">
-        <f t="shared" si="1"/>
-        <v>29.5</v>
+        <f>SUM(F73:I73)</f>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4088,12 +4073,12 @@
       <c r="H74" s="3">
         <v>12</v>
       </c>
-      <c r="I74" s="57">
-        <v>4.5</v>
+      <c r="I74" s="53">
+        <v>5</v>
       </c>
       <c r="J74" s="4">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
+        <f>SUM(F74:I74)</f>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4121,12 +4106,12 @@
       <c r="H75" s="3">
         <v>20</v>
       </c>
-      <c r="I75" s="57">
-        <v>6.5</v>
+      <c r="I75" s="53">
+        <v>7</v>
       </c>
       <c r="J75" s="4">
-        <f t="shared" si="1"/>
-        <v>39.25</v>
+        <f>SUM(F75:I75)</f>
+        <v>39.75</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4154,12 +4139,12 @@
       <c r="H76" s="3">
         <v>20</v>
       </c>
-      <c r="I76" s="57">
-        <v>8.5</v>
+      <c r="I76" s="53">
+        <v>9</v>
       </c>
       <c r="J76" s="4">
-        <f t="shared" si="1"/>
-        <v>40.75</v>
+        <f>SUM(F76:I76)</f>
+        <v>41.25</v>
       </c>
     </row>
     <row r="77" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4187,12 +4172,12 @@
       <c r="H77" s="3">
         <v>23</v>
       </c>
-      <c r="I77" s="57">
-        <v>7</v>
+      <c r="I77" s="53">
+        <v>7.5</v>
       </c>
       <c r="J77" s="4">
-        <f t="shared" si="1"/>
-        <v>43.5</v>
+        <f>SUM(F77:I77)</f>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4220,12 +4205,12 @@
       <c r="H78" s="3">
         <v>19</v>
       </c>
-      <c r="I78" s="57">
-        <v>3</v>
+      <c r="I78" s="53">
+        <v>3.5</v>
       </c>
       <c r="J78" s="4">
-        <f t="shared" si="1"/>
-        <v>31.5</v>
+        <f>SUM(F78:I78)</f>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4253,12 +4238,12 @@
       <c r="H79" s="3">
         <v>17</v>
       </c>
-      <c r="I79" s="57">
-        <v>9</v>
+      <c r="I79" s="53">
+        <v>9.5</v>
       </c>
       <c r="J79" s="4">
-        <f t="shared" si="1"/>
-        <v>38.5</v>
+        <f>SUM(F79:I79)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4286,12 +4271,12 @@
       <c r="H80" s="3">
         <v>21</v>
       </c>
-      <c r="I80" s="57">
-        <v>2</v>
+      <c r="I80" s="53">
+        <v>2.5</v>
       </c>
       <c r="J80" s="4">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f>SUM(F80:I80)</f>
+        <v>35.5</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4319,12 +4304,12 @@
       <c r="H81" s="3">
         <v>20</v>
       </c>
-      <c r="I81" s="57">
-        <v>4.5</v>
+      <c r="I81" s="53">
+        <v>5</v>
       </c>
       <c r="J81" s="4">
-        <f t="shared" si="1"/>
-        <v>37</v>
+        <f>SUM(F81:I81)</f>
+        <v>37.5</v>
       </c>
     </row>
     <row r="82" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4352,12 +4337,12 @@
       <c r="H82" s="3">
         <v>23</v>
       </c>
-      <c r="I82" s="57">
-        <v>10</v>
+      <c r="I82" s="53">
+        <v>10.5</v>
       </c>
       <c r="J82" s="4">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f>SUM(F82:I82)</f>
+        <v>47.5</v>
       </c>
     </row>
     <row r="83" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4385,12 +4370,12 @@
       <c r="H83" s="3">
         <v>22</v>
       </c>
-      <c r="I83" s="57">
-        <v>8.5</v>
+      <c r="I83" s="53">
+        <v>9</v>
       </c>
       <c r="J83" s="4">
-        <f t="shared" si="1"/>
-        <v>41.5</v>
+        <f>SUM(F83:I83)</f>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4416,12 +4401,12 @@
       <c r="H84" s="3">
         <v>18</v>
       </c>
-      <c r="I84" s="57">
-        <v>2.5</v>
+      <c r="I84" s="53">
+        <v>3</v>
       </c>
       <c r="J84" s="4">
-        <f t="shared" si="1"/>
-        <v>31.25</v>
+        <f>SUM(F84:I84)</f>
+        <v>31.75</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4449,12 +4434,12 @@
       <c r="H85" s="3">
         <v>24</v>
       </c>
-      <c r="I85" s="57">
-        <v>8.5</v>
+      <c r="I85" s="53">
+        <v>9</v>
       </c>
       <c r="J85" s="4">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f>SUM(F85:I85)</f>
+        <v>46.5</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4482,12 +4467,12 @@
       <c r="H86" s="3">
         <v>25</v>
       </c>
-      <c r="I86" s="57">
-        <v>8.5</v>
+      <c r="I86" s="53">
+        <v>9</v>
       </c>
       <c r="J86" s="4">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f>SUM(F86:I86)</f>
+        <v>47.5</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4515,12 +4500,12 @@
       <c r="H87" s="3">
         <v>25</v>
       </c>
-      <c r="I87" s="57">
-        <v>10</v>
+      <c r="I87" s="53">
+        <v>10.5</v>
       </c>
       <c r="J87" s="4">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f>SUM(F87:I87)</f>
+        <v>49.5</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4548,12 +4533,12 @@
       <c r="H88" s="3">
         <v>16</v>
       </c>
-      <c r="I88" s="57">
-        <v>8</v>
+      <c r="I88" s="53">
+        <v>8.5</v>
       </c>
       <c r="J88" s="4">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f>SUM(F88:I88)</f>
+        <v>35.5</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4581,12 +4566,12 @@
       <c r="H89" s="3">
         <v>16</v>
       </c>
-      <c r="I89" s="57">
-        <v>3.5</v>
+      <c r="I89" s="53">
+        <v>4</v>
       </c>
       <c r="J89" s="4">
-        <f t="shared" si="1"/>
-        <v>32</v>
+        <f>SUM(F89:I89)</f>
+        <v>32.5</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4614,12 +4599,12 @@
       <c r="H90" s="3">
         <v>21</v>
       </c>
-      <c r="I90" s="57">
-        <v>3</v>
+      <c r="I90" s="53">
+        <v>3.5</v>
       </c>
       <c r="J90" s="4">
-        <f t="shared" si="1"/>
-        <v>34.5</v>
+        <f>SUM(F90:I90)</f>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4647,12 +4632,12 @@
       <c r="H91" s="3">
         <v>17</v>
       </c>
-      <c r="I91" s="57">
-        <v>3</v>
+      <c r="I91" s="53">
+        <v>3.5</v>
       </c>
       <c r="J91" s="4">
-        <f t="shared" si="1"/>
-        <v>33.5</v>
+        <f>SUM(F91:I91)</f>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4678,12 +4663,12 @@
       <c r="H92" s="3">
         <v>17</v>
       </c>
-      <c r="I92" s="57">
-        <v>7</v>
+      <c r="I92" s="53">
+        <v>7.5</v>
       </c>
       <c r="J92" s="4">
-        <f t="shared" si="1"/>
-        <v>34.75</v>
+        <f>SUM(F92:I92)</f>
+        <v>35.25</v>
       </c>
     </row>
     <row r="93" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4703,7 +4688,7 @@
         <v>16</v>
       </c>
       <c r="F93" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G93" s="3">
         <v>4</v>
@@ -4711,12 +4696,12 @@
       <c r="H93" s="3">
         <v>14</v>
       </c>
-      <c r="I93" s="57">
-        <v>6.5</v>
+      <c r="I93" s="53">
+        <v>7</v>
       </c>
       <c r="J93" s="4">
-        <f t="shared" si="1"/>
-        <v>33.5</v>
+        <f>SUM(F93:I93)</f>
+        <v>34.5</v>
       </c>
     </row>
     <row r="94" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4744,12 +4729,12 @@
       <c r="H94" s="3">
         <v>23</v>
       </c>
-      <c r="I94" s="57">
-        <v>7</v>
+      <c r="I94" s="53">
+        <v>7.5</v>
       </c>
       <c r="J94" s="4">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f>SUM(F94:I94)</f>
+        <v>44.5</v>
       </c>
     </row>
     <row r="95" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4777,12 +4762,12 @@
       <c r="H95" s="3">
         <v>22</v>
       </c>
-      <c r="I95" s="57">
-        <v>10</v>
+      <c r="I95" s="53">
+        <v>10.5</v>
       </c>
       <c r="J95" s="4">
-        <f t="shared" si="1"/>
-        <v>46.5</v>
+        <f>SUM(F95:I95)</f>
+        <v>47</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4810,12 +4795,12 @@
       <c r="H96" s="3">
         <v>19</v>
       </c>
-      <c r="I96" s="57">
-        <v>3</v>
+      <c r="I96" s="53">
+        <v>3.5</v>
       </c>
       <c r="J96" s="4">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f>SUM(F96:I96)</f>
+        <v>34.5</v>
       </c>
     </row>
     <row r="97" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4843,12 +4828,12 @@
       <c r="H97" s="3">
         <v>22</v>
       </c>
-      <c r="I97" s="57">
-        <v>8.25</v>
+      <c r="I97" s="53">
+        <v>8.75</v>
       </c>
       <c r="J97" s="4">
-        <f t="shared" si="1"/>
-        <v>41.25</v>
+        <f>SUM(F97:I97)</f>
+        <v>41.75</v>
       </c>
     </row>
     <row r="98" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4874,12 +4859,12 @@
       <c r="H98" s="3">
         <v>23</v>
       </c>
-      <c r="I98" s="57">
-        <v>8</v>
+      <c r="I98" s="53">
+        <v>8.5</v>
       </c>
       <c r="J98" s="4">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>SUM(F98:I98)</f>
+        <v>42.5</v>
       </c>
     </row>
     <row r="99" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4907,12 +4892,12 @@
       <c r="H99" s="3">
         <v>22</v>
       </c>
-      <c r="I99" s="57">
-        <v>8.75</v>
+      <c r="I99" s="53">
+        <v>9.25</v>
       </c>
       <c r="J99" s="4">
-        <f t="shared" si="1"/>
-        <v>40.5</v>
+        <f>SUM(F99:I99)</f>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4940,12 +4925,12 @@
       <c r="H100" s="3">
         <v>18</v>
       </c>
-      <c r="I100" s="57">
-        <v>8.25</v>
+      <c r="I100" s="53">
+        <v>8.75</v>
       </c>
       <c r="J100" s="4">
-        <f t="shared" si="1"/>
-        <v>34.75</v>
+        <f>SUM(F100:I100)</f>
+        <v>35.25</v>
       </c>
     </row>
     <row r="101" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -4971,12 +4956,12 @@
       <c r="H101" s="3">
         <v>19</v>
       </c>
-      <c r="I101" s="57">
-        <v>2.5</v>
+      <c r="I101" s="53">
+        <v>3</v>
       </c>
       <c r="J101" s="4">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f>SUM(F101:I101)</f>
+        <v>35.5</v>
       </c>
     </row>
     <row r="102" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5002,12 +4987,12 @@
       <c r="H102" s="3">
         <v>22</v>
       </c>
-      <c r="I102" s="57">
-        <v>2.5</v>
+      <c r="I102" s="53">
+        <v>3</v>
       </c>
       <c r="J102" s="4">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f>SUM(F102:I102)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="103" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5035,12 +5020,12 @@
       <c r="H103" s="3">
         <v>23</v>
       </c>
-      <c r="I103" s="57">
-        <v>3</v>
+      <c r="I103" s="53">
+        <v>3.5</v>
       </c>
       <c r="J103" s="4">
-        <f t="shared" si="1"/>
-        <v>34.5</v>
+        <f>SUM(F103:I103)</f>
+        <v>35</v>
       </c>
     </row>
     <row r="104" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5068,12 +5053,12 @@
       <c r="H104" s="3">
         <v>20</v>
       </c>
-      <c r="I104" s="57">
-        <v>6.25</v>
+      <c r="I104" s="53">
+        <v>6.75</v>
       </c>
       <c r="J104" s="4">
-        <f t="shared" si="1"/>
-        <v>36.25</v>
+        <f>SUM(F104:I104)</f>
+        <v>36.75</v>
       </c>
     </row>
     <row r="105" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.45">
@@ -5099,12 +5084,12 @@
       <c r="H105" s="3">
         <v>23</v>
       </c>
-      <c r="I105" s="57">
-        <v>8.5</v>
+      <c r="I105" s="53">
+        <v>9</v>
       </c>
       <c r="J105" s="4">
-        <f t="shared" si="1"/>
-        <v>44.5</v>
+        <f>SUM(F105:I105)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5132,12 +5117,12 @@
       <c r="H106" s="3">
         <v>16</v>
       </c>
-      <c r="I106" s="57">
-        <v>6</v>
+      <c r="I106" s="53">
+        <v>6.5</v>
       </c>
       <c r="J106" s="4">
-        <f t="shared" si="1"/>
-        <v>33</v>
+        <f>SUM(F106:I106)</f>
+        <v>33.5</v>
       </c>
     </row>
     <row r="107" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5165,12 +5150,12 @@
       <c r="H107" s="3">
         <v>21</v>
       </c>
-      <c r="I107" s="57">
-        <v>5.5</v>
+      <c r="I107" s="53">
+        <v>6</v>
       </c>
       <c r="J107" s="4">
-        <f t="shared" si="1"/>
-        <v>37</v>
+        <f>SUM(F107:I107)</f>
+        <v>37.5</v>
       </c>
     </row>
     <row r="108" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5198,12 +5183,12 @@
       <c r="H108" s="3">
         <v>17</v>
       </c>
-      <c r="I108" s="57">
-        <v>8.25</v>
+      <c r="I108" s="53">
+        <v>8.75</v>
       </c>
       <c r="J108" s="4">
-        <f t="shared" si="1"/>
-        <v>36.5</v>
+        <f>SUM(F108:I108)</f>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5231,12 +5216,12 @@
       <c r="H109" s="3">
         <v>21</v>
       </c>
-      <c r="I109" s="57">
-        <v>8.75</v>
+      <c r="I109" s="53">
+        <v>9.25</v>
       </c>
       <c r="J109" s="4">
-        <f t="shared" si="1"/>
-        <v>41.5</v>
+        <f>SUM(F109:I109)</f>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5264,12 +5249,12 @@
       <c r="H110" s="3">
         <v>23</v>
       </c>
-      <c r="I110" s="57">
-        <v>8.75</v>
+      <c r="I110" s="53">
+        <v>9.25</v>
       </c>
       <c r="J110" s="4">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
+        <f>SUM(F110:I110)</f>
+        <v>43</v>
       </c>
     </row>
     <row r="111" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5297,12 +5282,12 @@
       <c r="H111" s="3">
         <v>22</v>
       </c>
-      <c r="I111" s="57">
-        <v>8</v>
+      <c r="I111" s="53">
+        <v>8.5</v>
       </c>
       <c r="J111" s="4">
-        <f t="shared" si="1"/>
-        <v>43.25</v>
+        <f>SUM(F111:I111)</f>
+        <v>43.75</v>
       </c>
     </row>
     <row r="112" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5330,12 +5315,12 @@
       <c r="H112" s="3">
         <v>21</v>
       </c>
-      <c r="I112" s="57">
-        <v>9.5</v>
+      <c r="I112" s="53">
+        <v>10</v>
       </c>
       <c r="J112" s="4">
-        <f t="shared" si="1"/>
-        <v>44</v>
+        <f>SUM(F112:I112)</f>
+        <v>44.5</v>
       </c>
     </row>
     <row r="113" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5363,12 +5348,12 @@
       <c r="H113" s="3">
         <v>25</v>
       </c>
-      <c r="I113" s="57">
-        <v>8.5</v>
+      <c r="I113" s="53">
+        <v>9</v>
       </c>
       <c r="J113" s="4">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f>SUM(F113:I113)</f>
+        <v>47.5</v>
       </c>
     </row>
     <row r="114" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5388,7 +5373,7 @@
         <v>16</v>
       </c>
       <c r="F114" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G114" s="3">
         <v>5</v>
@@ -5396,12 +5381,12 @@
       <c r="H114" s="3">
         <v>21</v>
       </c>
-      <c r="I114" s="57">
-        <v>2.5</v>
+      <c r="I114" s="53">
+        <v>3</v>
       </c>
       <c r="J114" s="4">
-        <f t="shared" si="1"/>
-        <v>37.5</v>
+        <f>SUM(F114:I114)</f>
+        <v>38.5</v>
       </c>
     </row>
     <row r="115" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5429,12 +5414,12 @@
       <c r="H115" s="3">
         <v>25</v>
       </c>
-      <c r="I115" s="57">
-        <v>7.5</v>
+      <c r="I115" s="53">
+        <v>8</v>
       </c>
       <c r="J115" s="4">
-        <f t="shared" si="1"/>
-        <v>44.25</v>
+        <f>SUM(F115:I115)</f>
+        <v>44.75</v>
       </c>
     </row>
     <row r="116" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5462,12 +5447,12 @@
       <c r="H116" s="3">
         <v>14</v>
       </c>
-      <c r="I116" s="57">
-        <v>8</v>
+      <c r="I116" s="53">
+        <v>8.5</v>
       </c>
       <c r="J116" s="4">
-        <f t="shared" si="1"/>
-        <v>33.25</v>
+        <f>SUM(F116:I116)</f>
+        <v>33.75</v>
       </c>
     </row>
     <row r="117" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5495,12 +5480,12 @@
       <c r="H117" s="3">
         <v>18</v>
       </c>
-      <c r="I117" s="57">
-        <v>4</v>
+      <c r="I117" s="53">
+        <v>4.5</v>
       </c>
       <c r="J117" s="4">
-        <f t="shared" si="1"/>
-        <v>33</v>
+        <f>SUM(F117:I117)</f>
+        <v>33.5</v>
       </c>
     </row>
     <row r="118" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5520,7 +5505,7 @@
         <v>16</v>
       </c>
       <c r="F118" s="4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G118" s="48">
         <v>3</v>
@@ -5528,12 +5513,12 @@
       <c r="H118" s="3">
         <v>24</v>
       </c>
-      <c r="I118" s="57">
-        <v>0.5</v>
+      <c r="I118" s="53">
+        <v>1</v>
       </c>
       <c r="J118" s="4">
-        <f t="shared" si="1"/>
-        <v>36.5</v>
+        <f>SUM(F118:I118)</f>
+        <v>37.5</v>
       </c>
     </row>
     <row r="119" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5561,12 +5546,12 @@
       <c r="H119" s="3">
         <v>24</v>
       </c>
-      <c r="I119" s="57">
-        <v>8.5</v>
+      <c r="I119" s="53">
+        <v>9</v>
       </c>
       <c r="J119" s="4">
-        <f t="shared" si="1"/>
-        <v>46.25</v>
+        <f>SUM(F119:I119)</f>
+        <v>46.75</v>
       </c>
     </row>
     <row r="120" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5592,12 +5577,12 @@
       <c r="H120" s="3">
         <v>21</v>
       </c>
-      <c r="I120" s="57">
-        <v>1.5</v>
+      <c r="I120" s="53">
+        <v>2</v>
       </c>
       <c r="J120" s="4">
-        <f t="shared" si="1"/>
-        <v>34.5</v>
+        <f>SUM(F120:I120)</f>
+        <v>35</v>
       </c>
     </row>
     <row r="121" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5625,12 +5610,12 @@
       <c r="H121" s="3">
         <v>21</v>
       </c>
-      <c r="I121" s="57">
-        <v>10</v>
+      <c r="I121" s="53">
+        <v>10.5</v>
       </c>
       <c r="J121" s="4">
-        <f t="shared" si="1"/>
-        <v>45.5</v>
+        <f>SUM(F121:I121)</f>
+        <v>46</v>
       </c>
     </row>
     <row r="122" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5658,12 +5643,12 @@
       <c r="H122" s="3">
         <v>17</v>
       </c>
-      <c r="I122" s="57">
-        <v>8.5</v>
+      <c r="I122" s="53">
+        <v>9</v>
       </c>
       <c r="J122" s="4">
-        <f t="shared" si="1"/>
-        <v>36.5</v>
+        <f>SUM(F122:I122)</f>
+        <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5691,12 +5676,12 @@
       <c r="H123" s="3">
         <v>23</v>
       </c>
-      <c r="I123" s="57">
-        <v>5</v>
+      <c r="I123" s="53">
+        <v>5.5</v>
       </c>
       <c r="J123" s="4">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f>SUM(F123:I123)</f>
+        <v>35.5</v>
       </c>
     </row>
     <row r="124" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5724,12 +5709,12 @@
       <c r="H124" s="3">
         <v>21</v>
       </c>
-      <c r="I124" s="57">
-        <v>9.25</v>
+      <c r="I124" s="53">
+        <v>9.75</v>
       </c>
       <c r="J124" s="4">
-        <f t="shared" si="1"/>
-        <v>39.5</v>
+        <f>SUM(F124:I124)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5757,12 +5742,12 @@
       <c r="H125" s="3">
         <v>17</v>
       </c>
-      <c r="I125" s="57">
-        <v>8</v>
+      <c r="I125" s="53">
+        <v>8.5</v>
       </c>
       <c r="J125" s="4">
-        <f t="shared" si="1"/>
-        <v>36.25</v>
+        <f>SUM(F125:I125)</f>
+        <v>36.75</v>
       </c>
     </row>
     <row r="126" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5790,12 +5775,12 @@
       <c r="H126" s="3">
         <v>22</v>
       </c>
-      <c r="I126" s="57">
-        <v>5</v>
+      <c r="I126" s="53">
+        <v>5.5</v>
       </c>
       <c r="J126" s="4">
-        <f t="shared" si="1"/>
-        <v>40.25</v>
+        <f>SUM(F126:I126)</f>
+        <v>40.75</v>
       </c>
     </row>
     <row r="127" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5823,12 +5808,12 @@
       <c r="H127" s="3">
         <v>19</v>
       </c>
-      <c r="I127" s="57">
-        <v>8.25</v>
+      <c r="I127" s="53">
+        <v>8.75</v>
       </c>
       <c r="J127" s="4">
-        <f t="shared" si="1"/>
-        <v>39.75</v>
+        <f>SUM(F127:I127)</f>
+        <v>40.25</v>
       </c>
     </row>
     <row r="128" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5854,12 +5839,12 @@
       <c r="H128" s="3">
         <v>18</v>
       </c>
-      <c r="I128" s="57">
-        <v>3.75</v>
+      <c r="I128" s="53">
+        <v>4.25</v>
       </c>
       <c r="J128" s="4">
-        <f t="shared" si="1"/>
-        <v>30.25</v>
+        <f>SUM(F128:I128)</f>
+        <v>30.75</v>
       </c>
     </row>
     <row r="129" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5887,12 +5872,12 @@
       <c r="H129" s="3">
         <v>17</v>
       </c>
-      <c r="I129" s="57">
-        <v>3</v>
+      <c r="I129" s="53">
+        <v>3.5</v>
       </c>
       <c r="J129" s="4">
-        <f t="shared" si="1"/>
-        <v>31.25</v>
+        <f>SUM(F129:I129)</f>
+        <v>31.75</v>
       </c>
     </row>
     <row r="130" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5920,12 +5905,12 @@
       <c r="H130" s="3">
         <v>15</v>
       </c>
-      <c r="I130" s="57">
-        <v>2.5</v>
+      <c r="I130" s="53">
+        <v>3</v>
       </c>
       <c r="J130" s="4">
-        <f t="shared" si="1"/>
-        <v>25.5</v>
+        <f>SUM(F130:I130)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5951,12 +5936,12 @@
       <c r="H131" s="3">
         <v>22</v>
       </c>
-      <c r="I131" s="57">
-        <v>4.5</v>
+      <c r="I131" s="53">
+        <v>5</v>
       </c>
       <c r="J131" s="4">
-        <f t="shared" ref="J131:J147" si="2">SUM(F131:I131)</f>
-        <v>36</v>
+        <f t="shared" ref="J131:J147" si="0">SUM(F131:I131)</f>
+        <v>36.5</v>
       </c>
     </row>
     <row r="132" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -5984,12 +5969,12 @@
       <c r="H132" s="3">
         <v>25</v>
       </c>
-      <c r="I132" s="57">
-        <v>8</v>
+      <c r="I132" s="53">
+        <v>8.5</v>
       </c>
       <c r="J132" s="4">
-        <f t="shared" si="2"/>
-        <v>46</v>
+        <f t="shared" si="0"/>
+        <v>46.5</v>
       </c>
     </row>
     <row r="133" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6017,12 +6002,12 @@
       <c r="H133" s="3">
         <v>24</v>
       </c>
-      <c r="I133" s="57">
-        <v>6.75</v>
+      <c r="I133" s="53">
+        <v>7.25</v>
       </c>
       <c r="J133" s="4">
-        <f t="shared" si="2"/>
-        <v>41.5</v>
+        <f t="shared" si="0"/>
+        <v>42</v>
       </c>
     </row>
     <row r="134" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6050,12 +6035,12 @@
       <c r="H134" s="3">
         <v>16</v>
       </c>
-      <c r="I134" s="57">
-        <v>8.5</v>
+      <c r="I134" s="53">
+        <v>9</v>
       </c>
       <c r="J134" s="4">
-        <f t="shared" si="2"/>
-        <v>36.5</v>
+        <f t="shared" si="0"/>
+        <v>37</v>
       </c>
     </row>
     <row r="135" spans="1:10" s="43" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6081,12 +6066,12 @@
       <c r="H135" s="39">
         <v>24</v>
       </c>
-      <c r="I135" s="58">
-        <v>5.75</v>
+      <c r="I135" s="53">
+        <v>6.25</v>
       </c>
       <c r="J135" s="42">
-        <f t="shared" si="2"/>
-        <v>35.75</v>
+        <f t="shared" si="0"/>
+        <v>36.25</v>
       </c>
     </row>
     <row r="136" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6114,12 +6099,12 @@
       <c r="H136" s="3">
         <v>23</v>
       </c>
-      <c r="I136" s="57">
-        <v>6</v>
+      <c r="I136" s="53">
+        <v>6.5</v>
       </c>
       <c r="J136" s="4">
-        <f t="shared" si="2"/>
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>40.5</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6147,12 +6132,12 @@
       <c r="H137" s="3">
         <v>23</v>
       </c>
-      <c r="I137" s="57">
-        <v>5.5</v>
+      <c r="I137" s="53">
+        <v>6</v>
       </c>
       <c r="J137" s="4">
-        <f t="shared" si="2"/>
-        <v>39.25</v>
+        <f t="shared" si="0"/>
+        <v>39.75</v>
       </c>
     </row>
     <row r="138" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6178,12 +6163,12 @@
       <c r="H138" s="3">
         <v>19</v>
       </c>
-      <c r="I138" s="57">
-        <v>8</v>
+      <c r="I138" s="53">
+        <v>8.5</v>
       </c>
       <c r="J138" s="4">
-        <f t="shared" si="2"/>
-        <v>38.5</v>
+        <f t="shared" si="0"/>
+        <v>39</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6211,12 +6196,12 @@
       <c r="H139" s="3">
         <v>19</v>
       </c>
-      <c r="I139" s="57">
-        <v>2.75</v>
+      <c r="I139" s="53">
+        <v>3.25</v>
       </c>
       <c r="J139" s="4">
-        <f t="shared" si="2"/>
-        <v>31.25</v>
+        <f t="shared" si="0"/>
+        <v>31.75</v>
       </c>
     </row>
     <row r="140" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6244,12 +6229,12 @@
       <c r="H140" s="3">
         <v>16</v>
       </c>
-      <c r="I140" s="57">
-        <v>5.5</v>
+      <c r="I140" s="53">
+        <v>6</v>
       </c>
       <c r="J140" s="4">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f t="shared" si="0"/>
+        <v>31.5</v>
       </c>
     </row>
     <row r="141" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6277,12 +6262,12 @@
       <c r="H141" s="3">
         <v>19</v>
       </c>
-      <c r="I141" s="57">
-        <v>7.5</v>
+      <c r="I141" s="53">
+        <v>8</v>
       </c>
       <c r="J141" s="4">
-        <f t="shared" si="2"/>
-        <v>39.75</v>
+        <f t="shared" si="0"/>
+        <v>40.25</v>
       </c>
     </row>
     <row r="142" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6310,12 +6295,12 @@
       <c r="H142" s="3">
         <v>23</v>
       </c>
-      <c r="I142" s="57">
-        <v>9.75</v>
+      <c r="I142" s="53">
+        <v>10.25</v>
       </c>
       <c r="J142" s="4">
-        <f t="shared" si="2"/>
-        <v>44.5</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
     </row>
     <row r="143" spans="1:10" s="1" customFormat="1" ht="21.65" customHeight="1" x14ac:dyDescent="0.5">
@@ -6343,12 +6328,12 @@
       <c r="H143" s="3">
         <v>24</v>
       </c>
-      <c r="I143" s="57">
-        <v>7.25</v>
+      <c r="I143" s="53">
+        <v>7.75</v>
       </c>
       <c r="J143" s="4">
-        <f t="shared" si="2"/>
-        <v>42.5</v>
+        <f t="shared" si="0"/>
+        <v>43</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -6376,12 +6361,12 @@
       <c r="H144" s="3">
         <v>23</v>
       </c>
-      <c r="I144" s="57">
-        <v>3.5</v>
+      <c r="I144" s="53">
+        <v>4</v>
       </c>
       <c r="J144" s="4">
-        <f t="shared" si="2"/>
-        <v>39.75</v>
+        <f t="shared" si="0"/>
+        <v>40.25</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -6409,12 +6394,12 @@
       <c r="H145" s="3">
         <v>21</v>
       </c>
-      <c r="I145" s="57">
-        <v>8.75</v>
+      <c r="I145" s="53">
+        <v>9.25</v>
       </c>
       <c r="J145" s="4">
-        <f t="shared" si="2"/>
-        <v>41</v>
+        <f t="shared" si="0"/>
+        <v>41.5</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -6442,12 +6427,12 @@
       <c r="H146" s="3">
         <v>16</v>
       </c>
-      <c r="I146" s="57">
-        <v>6.25</v>
+      <c r="I146" s="53">
+        <v>6.75</v>
       </c>
       <c r="J146" s="4">
-        <f t="shared" si="2"/>
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>34.5</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="21" x14ac:dyDescent="0.5">
@@ -6473,12 +6458,12 @@
       <c r="H147" s="3">
         <v>16</v>
       </c>
-      <c r="I147" s="57">
-        <v>7.5</v>
+      <c r="I147" s="53">
+        <v>8</v>
       </c>
       <c r="J147" s="4">
-        <f t="shared" si="2"/>
-        <v>36.25</v>
+        <f t="shared" si="0"/>
+        <v>36.75</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
